--- a/Analysed/Gemini_gemini-3-pro-preview_naive.xlsx
+++ b/Analysed/Gemini_gemini-3-pro-preview_naive.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H2" t="n">
-        <v>2.452173913043478</v>
+        <v>2.466184615384616</v>
       </c>
       <c r="I2" t="n">
-        <v>2.620583951802958</v>
+        <v>2.636200587675668</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09345794392523364</v>
+        <v>0.1018518518518518</v>
       </c>
     </row>
     <row r="3">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H4" t="n">
-        <v>1.389449541284403</v>
+        <v>1.380357142857143</v>
       </c>
       <c r="I4" t="n">
-        <v>1.682255203233843</v>
+        <v>1.668446133382795</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.03603603603603604</v>
       </c>
     </row>
     <row r="5">
@@ -693,10 +693,10 @@
         <v>51</v>
       </c>
       <c r="H6" t="n">
-        <v>2.539607843137255</v>
+        <v>2.541764705882353</v>
       </c>
       <c r="I6" t="n">
-        <v>2.796649956714668</v>
+        <v>2.79973703246937</v>
       </c>
       <c r="J6" t="n">
         <v>0.38</v>
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7224698795180723</v>
+        <v>0.7161791044776119</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8629443154493024</v>
+        <v>0.8590737809955731</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1148036253776435</v>
+        <v>0.1227544910179641</v>
       </c>
     </row>
     <row r="9">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4339774011299435</v>
+        <v>0.4348826815642458</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5016377922129384</v>
+        <v>0.5017890673942832</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4204545454545455</v>
+        <v>0.4157303370786517</v>
       </c>
     </row>
     <row r="10">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5774666666666666</v>
+        <v>0.5627272727272726</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7999808331037273</v>
+        <v>0.7895247625308219</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3648648648648649</v>
+        <v>0.3815789473684211</v>
       </c>
     </row>
     <row r="12">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H12" t="n">
-        <v>3.443859649122807</v>
+        <v>3.46271186440678</v>
       </c>
       <c r="I12" t="n">
-        <v>3.491832575717528</v>
+        <v>3.510263402159783</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4464285714285715</v>
+        <v>0.4655172413793103</v>
       </c>
     </row>
     <row r="13">
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H14" t="n">
-        <v>1.495329153605016</v>
+        <v>1.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.751424409106784</v>
+        <v>1.756655736050749</v>
       </c>
       <c r="J14" t="n">
-        <v>0.06289308176100629</v>
+        <v>0.06583072100313479</v>
       </c>
     </row>
     <row r="15">
@@ -1218,16 +1218,16 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H18" t="n">
-        <v>1.576862745098039</v>
+        <v>1.605</v>
       </c>
       <c r="I18" t="n">
-        <v>1.968473081987611</v>
+        <v>1.994515557144719</v>
       </c>
       <c r="J18" t="n">
-        <v>0.38</v>
+        <v>0.392156862745098</v>
       </c>
     </row>
     <row r="19">
@@ -1438,16 +1438,16 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H23" t="n">
-        <v>17.82513513513513</v>
+        <v>17.75868421052631</v>
       </c>
       <c r="I23" t="n">
-        <v>17.9605618253183</v>
+        <v>17.89561538478071</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5277777777777778</v>
+        <v>0.5405405405405406</v>
       </c>
     </row>
     <row r="24">
@@ -1570,16 +1570,16 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H26" t="n">
-        <v>16.17754098360656</v>
+        <v>16.15048</v>
       </c>
       <c r="I26" t="n">
-        <v>16.19851576888309</v>
+        <v>16.17190672740849</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2231404958677686</v>
+        <v>0.2419354838709677</v>
       </c>
     </row>
     <row r="27">
@@ -1878,16 +1878,16 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H33" t="n">
-        <v>17.98030303030303</v>
+        <v>18.12428571428572</v>
       </c>
       <c r="I33" t="n">
-        <v>18.06715335361468</v>
+        <v>18.21492872814573</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2753623188405797</v>
       </c>
     </row>
     <row r="34">
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H37" t="n">
-        <v>14.51052631578947</v>
+        <v>16.16060606060606</v>
       </c>
       <c r="I37" t="n">
-        <v>14.6645472950385</v>
+        <v>16.35382449941223</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="38">
@@ -2186,16 +2186,16 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H40" t="n">
-        <v>18.57962962962963</v>
+        <v>18.99272727272727</v>
       </c>
       <c r="I40" t="n">
-        <v>22.76566908502557</v>
+        <v>23.23499601893661</v>
       </c>
       <c r="J40" t="n">
-        <v>0.02803738317757009</v>
+        <v>0.04587155963302753</v>
       </c>
     </row>
     <row r="41">
@@ -2230,16 +2230,16 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H41" t="n">
-        <v>43.15769230769231</v>
+        <v>44.50375</v>
       </c>
       <c r="I41" t="n">
-        <v>52.85325718318404</v>
+        <v>54.39541685656982</v>
       </c>
       <c r="J41" t="n">
-        <v>0.02597402597402598</v>
+        <v>0.02531645569620253</v>
       </c>
     </row>
     <row r="42">
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H42" t="n">
-        <v>11.11488372093024</v>
+        <v>11.78977777777778</v>
       </c>
       <c r="I42" t="n">
-        <v>14.07377736438677</v>
+        <v>14.83272807753928</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="43">
@@ -2318,13 +2318,13 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H43" t="n">
-        <v>23.35678571428571</v>
+        <v>24.54515151515152</v>
       </c>
       <c r="I43" t="n">
-        <v>26.80538851744978</v>
+        <v>27.52877717457266</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2362,16 +2362,16 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H44" t="n">
-        <v>21.77314814814815</v>
+        <v>21.75107692307692</v>
       </c>
       <c r="I44" t="n">
-        <v>22.26055854345678</v>
+        <v>22.24103478500253</v>
       </c>
       <c r="J44" t="n">
-        <v>0.07739938080495357</v>
+        <v>0.08024691358024691</v>
       </c>
     </row>
     <row r="45">
@@ -2402,20 +2402,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>116</v>
+        <v>209</v>
       </c>
       <c r="H45" t="n">
-        <v>21.94137931034483</v>
+        <v>11.13564593301436</v>
       </c>
       <c r="I45" t="n">
-        <v>22.52913933033211</v>
+        <v>13.00021392904582</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.4471153846153846</v>
       </c>
     </row>
     <row r="46">
@@ -2446,20 +2446,20 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="H46" t="n">
-        <v>18.28764705882353</v>
+        <v>21.94137931034483</v>
       </c>
       <c r="I46" t="n">
-        <v>19.04853574733888</v>
+        <v>22.52913933033211</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.2173913043478261</v>
       </c>
     </row>
     <row r="47">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="H47" t="n">
-        <v>21.46272727272726</v>
+        <v>18.28764705882353</v>
       </c>
       <c r="I47" t="n">
-        <v>22.20400262851886</v>
+        <v>19.04853574733888</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.2619047619047619</v>
       </c>
     </row>
     <row r="48">
@@ -2534,20 +2534,20 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H48" t="n">
-        <v>21.70357142857143</v>
+        <v>21.46272727272726</v>
       </c>
       <c r="I48" t="n">
-        <v>25.49309444311762</v>
+        <v>22.20400262851886</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.4074074074074074</v>
       </c>
     </row>
     <row r="49">
@@ -2573,25 +2573,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OPENING</t>
+          <t>OPENING-CLOSING</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>315</v>
+        <v>42</v>
       </c>
       <c r="H49" t="n">
-        <v>26.09380952380952</v>
+        <v>21.70357142857143</v>
       </c>
       <c r="I49" t="n">
-        <v>27.6252078639023</v>
+        <v>25.49309444311762</v>
       </c>
       <c r="J49" t="n">
-        <v>0.04458598726114649</v>
+        <v>0.5365853658536586</v>
       </c>
     </row>
     <row r="50">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>193</v>
+        <v>315</v>
       </c>
       <c r="H50" t="n">
-        <v>26.10181347150259</v>
+        <v>26.09380952380952</v>
       </c>
       <c r="I50" t="n">
-        <v>27.69486079596307</v>
+        <v>27.6252078639023</v>
       </c>
       <c r="J50" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.04458598726114649</v>
       </c>
     </row>
     <row r="51">
@@ -2666,20 +2666,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="H51" t="n">
-        <v>26.21714285714285</v>
+        <v>26.26076923076923</v>
       </c>
       <c r="I51" t="n">
-        <v>27.98415401956036</v>
+        <v>27.87270935281797</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1346153846153846</v>
+        <v>0.06701030927835051</v>
       </c>
     </row>
     <row r="52">
@@ -2710,20 +2710,20 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
+          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="H52" t="n">
-        <v>8.717631578947367</v>
+        <v>26.21714285714285</v>
       </c>
       <c r="I52" t="n">
-        <v>9.878472740470084</v>
+        <v>27.98415401956036</v>
       </c>
       <c r="J52" t="n">
-        <v>0.84</v>
+        <v>0.1346153846153846</v>
       </c>
     </row>
     <row r="53">
@@ -2754,20 +2754,20 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="H53" t="n">
-        <v>24.02391304347826</v>
+        <v>8.717631578947367</v>
       </c>
       <c r="I53" t="n">
-        <v>24.85418913163944</v>
+        <v>9.878472740470084</v>
       </c>
       <c r="J53" t="n">
-        <v>0.8222222222222222</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="54">
@@ -2798,19 +2798,63 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>46</v>
+      </c>
+      <c r="H54" t="n">
+        <v>24.02391304347826</v>
+      </c>
+      <c r="I54" t="n">
+        <v>24.85418913163944</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.8222222222222222</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>gemini-3-pro-preview</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>naive</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3.- Analog Depth Gauge_without vernier</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>OPENING_OPENING_V6_10 divisions_per_second</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="G55" t="n">
         <v>31</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H55" t="n">
         <v>20.36451612903225</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I55" t="n">
         <v>20.67635411175865</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J55" t="n">
         <v>0.9333333333333333</v>
       </c>
     </row>
@@ -2857,14 +2901,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.5529</v>
+        <v>13.61</v>
       </c>
       <c r="C2" t="n">
-        <v>10.8297</v>
+        <v>10.8345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.5529 ± 10.8297</t>
+          <t>13.6100 ± 10.8345</t>
         </is>
       </c>
     </row>
@@ -2875,14 +2919,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.3688</v>
+        <v>14.4442</v>
       </c>
       <c r="C3" t="n">
-        <v>11.6951</v>
+        <v>11.7117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14.3688 ± 11.6951</t>
+          <t>14.4442 ± 11.7117</t>
         </is>
       </c>
     </row>
@@ -2893,14 +2937,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3449</v>
+        <v>0.3532</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2654</v>
+        <v>0.266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.3449 ± 0.2654</t>
+          <t>0.3532 ± 0.2660</t>
         </is>
       </c>
     </row>
@@ -2975,19 +3019,19 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1217</v>
+        <v>2.1229</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8585</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3964</v>
+        <v>2.3972</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2463</v>
+        <v>0.2475</v>
       </c>
       <c r="H2" t="n">
-        <v>125.8</v>
+        <v>126.8</v>
       </c>
     </row>
     <row r="3">
@@ -3005,19 +3049,19 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4575</v>
+        <v>1.463</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2549</v>
+        <v>0.2582</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7763</v>
+        <v>1.7815</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3461</v>
+        <v>0.3486</v>
       </c>
       <c r="H3" t="n">
-        <v>124.2</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="4">
@@ -3035,19 +3079,19 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0609</v>
+        <v>1.0607</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2301</v>
+        <v>1.2397</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2161</v>
+        <v>1.2168</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3493</v>
+        <v>0.3558</v>
       </c>
       <c r="H4" t="n">
-        <v>132.7</v>
+        <v>134.2</v>
       </c>
     </row>
     <row r="5">
@@ -3065,19 +3109,19 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>14.1132</v>
+        <v>14.1021</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6129</v>
+        <v>5.6033</v>
       </c>
       <c r="F5" t="n">
-        <v>14.3245</v>
+        <v>14.3137</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3199</v>
+        <v>0.322</v>
       </c>
       <c r="H5" t="n">
-        <v>55.2</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="6">
@@ -3095,19 +3139,19 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>21.0901</v>
+        <v>21.3891</v>
       </c>
       <c r="E6" t="n">
-        <v>11.3919</v>
+        <v>11.1929</v>
       </c>
       <c r="F6" t="n">
-        <v>21.1708</v>
+        <v>21.477</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4736</v>
+        <v>0.5053</v>
       </c>
       <c r="H6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -3125,19 +3169,19 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>14.9272</v>
+        <v>14.9226</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6196</v>
+        <v>1.615</v>
       </c>
       <c r="F7" t="n">
-        <v>14.9589</v>
+        <v>14.9545</v>
       </c>
       <c r="G7" t="n">
-        <v>0.515</v>
+        <v>0.5181</v>
       </c>
       <c r="H7" t="n">
-        <v>61.7</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="8">
@@ -3155,19 +3199,19 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>25.4987</v>
+        <v>26.1025</v>
       </c>
       <c r="E8" t="n">
-        <v>11.4172</v>
+        <v>11.5988</v>
       </c>
       <c r="F8" t="n">
-        <v>29.3734</v>
+        <v>29.9557</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>128.7</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="9">
@@ -3185,19 +3229,19 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>21.9198</v>
+        <v>21.9463</v>
       </c>
       <c r="E9" t="n">
-        <v>7.1873</v>
+        <v>7.2079</v>
       </c>
       <c r="F9" t="n">
-        <v>23.1189</v>
+        <v>23.1485</v>
       </c>
       <c r="G9" t="n">
-        <v>0.472</v>
+        <v>0.4736</v>
       </c>
       <c r="H9" t="n">
-        <v>127.7</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -3212,22 +3256,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>21.0337</v>
+        <v>19.3803</v>
       </c>
       <c r="E10" t="n">
-        <v>1.918</v>
+        <v>4.4791</v>
       </c>
       <c r="F10" t="n">
-        <v>22.3071</v>
+        <v>20.7527</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3001</v>
+        <v>0.3251</v>
       </c>
       <c r="H10" t="n">
-        <v>124.4</v>
+        <v>138.7</v>
       </c>
     </row>
   </sheetData>
